--- a/backend/src/OrderMgmt.WebApi/templates/templete_bbbg_sl.xlsx
+++ b/backend/src/OrderMgmt.WebApi/templates/templete_bbbg_sl.xlsx
@@ -179,7 +179,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -228,12 +228,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -295,29 +304,32 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1406,64 +1418,67 @@
       <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:8" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
     </row>
     <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
     </row>
     <row r="9" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="31" t="s">
         <v>6</v>
       </c>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
     </row>
     <row r="13" spans="1:8" s="9" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -1510,10 +1525,10 @@
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14"/>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="30"/>
+      <c r="C16" s="23"/>
       <c r="D16" s="15"/>
       <c r="E16" s="16"/>
       <c r="G16" s="18"/>
@@ -1532,63 +1547,64 @@
       <c r="A18" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
       <c r="H18" s="22"/>
     </row>
     <row r="19" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
     </row>
     <row r="21" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="24"/>
+      <c r="B21" s="29"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="25"/>
+      <c r="E21" s="30"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E24" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B6:E7"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.25" top="0.5" bottom="0.75" header="0.05" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/backend/src/OrderMgmt.WebApi/templates/templete_bbbg_sl.xlsx
+++ b/backend/src/OrderMgmt.WebApi/templates/templete_bbbg_sl.xlsx
@@ -304,6 +304,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -317,16 +326,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1418,56 +1418,56 @@
       <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:8" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
     </row>
     <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="10" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
@@ -1525,10 +1525,10 @@
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14"/>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="23"/>
+      <c r="C16" s="26"/>
       <c r="D16" s="15"/>
       <c r="E16" s="16"/>
       <c r="G16" s="18"/>
@@ -1547,57 +1547,52 @@
       <c r="A18" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
       <c r="H18" s="22"/>
     </row>
     <row r="19" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
     </row>
     <row r="21" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="29"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="30"/>
+      <c r="E21" s="25"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E24" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B6:E7"/>
     <mergeCell ref="A8:E8"/>
@@ -1605,6 +1600,11 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.25" top="0.5" bottom="0.75" header="0.05" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/backend/src/OrderMgmt.WebApi/templates/templete_bbbg_sl.xlsx
+++ b/backend/src/OrderMgmt.WebApi/templates/templete_bbbg_sl.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -304,32 +304,32 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1418,67 +1418,67 @@
       <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:8" ht="6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
     </row>
     <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
     </row>
     <row r="9" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:8" s="9" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -1514,7 +1514,7 @@
     </row>
     <row r="15" spans="1:8" s="9" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>13</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14"/>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="26"/>
+      <c r="C16" s="23"/>
       <c r="D16" s="15"/>
       <c r="E16" s="16"/>
       <c r="G16" s="18"/>
@@ -1547,52 +1547,57 @@
       <c r="A18" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
       <c r="H18" s="22"/>
     </row>
     <row r="19" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
     </row>
     <row r="20" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
     </row>
     <row r="21" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="24"/>
+      <c r="B21" s="30"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="25"/>
+      <c r="E21" s="31"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E24" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B6:E7"/>
     <mergeCell ref="A8:E8"/>
@@ -1600,11 +1605,6 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.25" top="0.5" bottom="0.75" header="0.05" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
